--- a/tame_output/ON/bt/strategyON_20240215.xlsx
+++ b/tame_output/ON/bt/strategyON_20240215.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.6%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>76.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -773,11 +773,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-1.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>98.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.2%</t>
+          <t>-155.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>127.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1873"/>
+  <dimension ref="A1:G1874"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447852901079075</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44640,6 +44640,29 @@
       </c>
       <c r="G1873" t="n">
         <v>4.470159868768729</v>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" s="2" t="n">
+        <v>45336</v>
+      </c>
+      <c r="B1874" t="n">
+        <v>3.506593302686997</v>
+      </c>
+      <c r="C1874" t="n">
+        <v>3.120955568236086</v>
+      </c>
+      <c r="D1874" t="n">
+        <v>1.600256306696806</v>
+      </c>
+      <c r="E1874" t="n">
+        <v>3.760701666601061</v>
+      </c>
+      <c r="F1874" t="n">
+        <v>2.257591006384487</v>
+      </c>
+      <c r="G1874" t="n">
+        <v>4.475510172066778</v>
       </c>
     </row>
   </sheetData>
